--- a/artfynd/A 8514-2022 artfynd.xlsx
+++ b/artfynd/A 8514-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8514-2022 artfynd.xlsx
+++ b/artfynd/A 8514-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,6 +1681,213 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128186212</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>406853</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6715478</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4 st uppflygande</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128186213</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>406855</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6715492</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8514-2022 artfynd.xlsx
+++ b/artfynd/A 8514-2022 artfynd.xlsx
@@ -1796,7 +1796,7 @@
         <v>128186213</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8514-2022 artfynd.xlsx
+++ b/artfynd/A 8514-2022 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>128186212</v>
       </c>
       <c r="B11" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>128186213</v>
       </c>
       <c r="B12" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8514-2022 artfynd.xlsx
+++ b/artfynd/A 8514-2022 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>128186212</v>
       </c>
       <c r="B11" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>128186213</v>
       </c>
       <c r="B12" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8514-2022 artfynd.xlsx
+++ b/artfynd/A 8514-2022 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>128186212</v>
       </c>
       <c r="B11" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>128186213</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8514-2022 artfynd.xlsx
+++ b/artfynd/A 8514-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104424828</v>
+        <v>104424298</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Häståsen, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406928.3397682405</v>
+        <v>406850</v>
       </c>
       <c r="R2" t="n">
-        <v>6715570.369052334</v>
+        <v>6715584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104424831</v>
+        <v>104424300</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -823,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häståsen, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406773.723410499</v>
+        <v>406868</v>
       </c>
       <c r="R3" t="n">
-        <v>6715440.563582879</v>
+        <v>6715554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104424825</v>
+        <v>104424303</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Häståsen, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406927.3905580389</v>
+        <v>406770</v>
       </c>
       <c r="R4" t="n">
-        <v>6715648.113319596</v>
+        <v>6715442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,49 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104424826</v>
+        <v>104424824</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406930.5934805865</v>
+        <v>406917</v>
       </c>
       <c r="R5" t="n">
-        <v>6715619.500790333</v>
+        <v>6715676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104424300</v>
+        <v>104424827</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1159,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Häståsen, Åskakskölen, Vrm</t>
+          <t>Häståsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406867.3332157518</v>
+        <v>406930</v>
       </c>
       <c r="R6" t="n">
-        <v>6715554.727790667</v>
+        <v>6715619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,12 +1148,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1238,16 +1163,11 @@
         <v>104424829</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406925.2053134439</v>
+        <v>406925</v>
       </c>
       <c r="R7" t="n">
-        <v>6715544.379040854</v>
+        <v>6715544</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104424299</v>
+        <v>104424831</v>
       </c>
       <c r="B8" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häståsen, Åskakskölen, Vrm</t>
+          <t>Häståsen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406869.2420758848</v>
+        <v>406774</v>
       </c>
       <c r="R8" t="n">
-        <v>6715571.403218209</v>
+        <v>6715440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,31 +1342,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104424827</v>
+        <v>104424834</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406930.5934805865</v>
+        <v>406576</v>
       </c>
       <c r="R9" t="n">
-        <v>6715619.500790333</v>
+        <v>6715296</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104424303</v>
+        <v>104424825</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Häståsen, Åskakskölen, Vrm</t>
+          <t>Häståsen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406769.8351122644</v>
+        <v>406927</v>
       </c>
       <c r="R10" t="n">
-        <v>6715442.631806949</v>
+        <v>6715648</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,65 +1536,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128186212</v>
+        <v>104424833</v>
       </c>
       <c r="B11" t="n">
-        <v>56907</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Häståsen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406853</v>
+        <v>406692</v>
       </c>
       <c r="R11" t="n">
-        <v>6715478</v>
+        <v>6715384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,17 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4 st uppflygande</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,57 +1633,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128186213</v>
+        <v>128186212</v>
       </c>
       <c r="B12" t="n">
-        <v>57876</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406855</v>
+        <v>406853</v>
       </c>
       <c r="R12" t="n">
-        <v>6715492</v>
+        <v>6715478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,6 +1726,11 @@
           <t>2025-08-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4 st uppflygande</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1887,6 +1752,491 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128186213</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>406855</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6715492</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128186214</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>406792</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6715530</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104424299</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Häståsen, Åskakskölen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>406869</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6715572</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104424826</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Häståsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>406930</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6715619</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104424828</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Häståsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>406928</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6715570</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8514-2022 artfynd.xlsx
+++ b/artfynd/A 8514-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424298</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424300</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424303</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424824</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424827</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424829</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424831</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424834</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424825</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424833</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128186212</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128186213</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128186214</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424299</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2140,6 +2215,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424826</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,8 +2317,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424828</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>